--- a/histograms/histogram_Surface_area__m2_g.xlsx
+++ b/histograms/histogram_Surface_area__m2_g.xlsx
@@ -445,7 +445,7 @@
         <v>5.395</v>
       </c>
       <c r="B2" t="n">
-        <v>19319</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>15.785</v>
       </c>
       <c r="B3" t="n">
-        <v>1490</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>26.175</v>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>36.565</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>46.95500000000001</v>
       </c>
       <c r="B6" t="n">
-        <v>2120</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>57.34500000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>2022</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>67.73500000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>442</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>78.125</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>88.51500000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>98.905</v>
       </c>
       <c r="B11" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>109.295</v>
       </c>
       <c r="B12" t="n">
-        <v>225</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>119.685</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -549,7 +549,7 @@
         <v>140.465</v>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -597,7 +597,7 @@
         <v>202.805</v>
       </c>
       <c r="B21" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
